--- a/template/北二區週報_優化.xlsx
+++ b/template/北二區週報_優化.xlsx
@@ -24635,7 +24635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF42"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" style="83" min="1" max="1"/>
@@ -24688,6 +24688,8 @@
       <c r="AD1" s="135" t="n"/>
       <c r="AE1" s="135" t="n"/>
       <c r="AF1" s="135" t="n"/>
+      <c r="AG1" s="135" t="n"/>
+      <c r="AH1" s="135" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="83">
       <c r="A2" s="72" t="n"/>
@@ -24737,51 +24739,61 @@
       <c r="U2" s="72" t="n"/>
       <c r="V2" s="72" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="W2" s="72" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="X2" s="72" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="72" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="72" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="AA2" s="72" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="AB2" s="72" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AC2" s="72" t="n"/>
+      <c r="AD2" s="72" t="n"/>
+      <c r="AE2" s="72" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="W2" s="72" t="inlineStr">
+      <c r="AF2" s="72" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="X2" s="72" t="inlineStr">
+      <c r="AG2" s="72" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="Y2" s="72" t="inlineStr">
+      <c r="AH2" s="72" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="Z2" s="72" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="AA2" s="72" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="AB2" s="72" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AC2" s="72" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AD2" s="72" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AE2" s="72" t="n"/>
-      <c r="AF2" s="72" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -24901,49 +24913,61 @@
           <t>較上月比</t>
         </is>
       </c>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
-      <c r="X3" s="86" t="n"/>
-      <c r="Y3" s="86" t="n"/>
-      <c r="Z3" s="70" t="inlineStr">
+      <c r="V3" s="70" t="inlineStr">
         <is>
           <t>3PP搭售率
 上月</t>
         </is>
       </c>
-      <c r="AA3" s="71" t="inlineStr">
+      <c r="W3" s="71" t="inlineStr">
         <is>
           <t>3PP搭售率
 本月</t>
         </is>
       </c>
-      <c r="AB3" s="75" t="inlineStr">
+      <c r="X3" s="75" t="inlineStr">
         <is>
           <t>SACARE搭售率
 上月</t>
         </is>
       </c>
-      <c r="AC3" s="76" t="inlineStr">
+      <c r="Y3" s="76" t="inlineStr">
         <is>
           <t>SACARE搭售率
 本月</t>
         </is>
       </c>
-      <c r="AD3" s="39" t="inlineStr">
+      <c r="Z3" s="75" t="inlineStr">
+        <is>
+          <t>AC搭售率
+上月</t>
+        </is>
+      </c>
+      <c r="AA3" s="76" t="inlineStr">
+        <is>
+          <t>AC搭售率
+本月</t>
+        </is>
+      </c>
+      <c r="AB3" s="39" t="inlineStr">
         <is>
           <t>上月</t>
         </is>
       </c>
-      <c r="AE3" s="40" t="inlineStr">
+      <c r="AC3" s="40" t="inlineStr">
         <is>
           <t>本月</t>
         </is>
       </c>
-      <c r="AF3" s="86" t="inlineStr">
+      <c r="AD3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
+      <c r="AG3" s="86" t="n"/>
+      <c r="AH3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="73" t="inlineStr">
@@ -25007,35 +25031,41 @@
       <c r="U4" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="123" t="n"/>
-      <c r="Y4" s="123" t="n"/>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AA4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="123" t="n">
+      <c r="AB4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AF4" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="123" t="n"/>
+      <c r="AH4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="73" t="inlineStr">
@@ -25099,35 +25129,41 @@
       <c r="U5" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="124" t="n"/>
-      <c r="Y5" s="124" t="n"/>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="124" t="n">
+      <c r="AB5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="124" t="n"/>
+      <c r="AH5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="73" t="inlineStr">
@@ -25191,35 +25227,41 @@
       <c r="U6" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="123" t="n"/>
-      <c r="Y6" s="123" t="n"/>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="Z6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="123" t="n">
+      <c r="AB6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AF6" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="123" t="n"/>
+      <c r="AH6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="73" t="inlineStr">
@@ -25283,35 +25325,41 @@
       <c r="U7" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="124" t="n"/>
-      <c r="Y7" s="124" t="n"/>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Z7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="124" t="n">
+      <c r="AB7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AF7" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="124" t="n"/>
+      <c r="AH7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="73" t="inlineStr">
@@ -25375,35 +25423,41 @@
       <c r="U8" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="123" t="n"/>
-      <c r="Y8" s="123" t="n"/>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="Z8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="123" t="n">
+      <c r="AB8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AF8" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="123" t="n"/>
+      <c r="AH8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="73" t="inlineStr">
@@ -25467,35 +25521,41 @@
       <c r="U9" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="124" t="n"/>
-      <c r="Y9" s="124" t="n"/>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Z9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="124" t="n">
+      <c r="AB9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="124" t="n"/>
+      <c r="AH9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="73" t="n"/>
@@ -25519,17 +25579,19 @@
       <c r="S10" s="124" t="n"/>
       <c r="T10" s="124" t="n"/>
       <c r="U10" s="74" t="n"/>
-      <c r="V10" s="124" t="n"/>
-      <c r="W10" s="124" t="n"/>
-      <c r="X10" s="124" t="n"/>
-      <c r="Y10" s="124" t="n"/>
+      <c r="V10" s="46" t="n"/>
+      <c r="W10" s="46" t="n"/>
+      <c r="X10" s="46" t="n"/>
+      <c r="Y10" s="46" t="n"/>
       <c r="Z10" s="46" t="n"/>
       <c r="AA10" s="46" t="n"/>
-      <c r="AB10" s="46" t="n"/>
-      <c r="AC10" s="46" t="n"/>
-      <c r="AD10" s="124" t="n"/>
+      <c r="AB10" s="124" t="n"/>
+      <c r="AC10" s="124" t="n"/>
+      <c r="AD10" s="74" t="n"/>
       <c r="AE10" s="124" t="n"/>
-      <c r="AF10" s="74" t="n"/>
+      <c r="AF10" s="124" t="n"/>
+      <c r="AG10" s="124" t="n"/>
+      <c r="AH10" s="124" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="83">
       <c r="A11" s="47" t="inlineStr">
@@ -25593,35 +25655,41 @@
       <c r="U11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="125" t="n"/>
-      <c r="Y11" s="125" t="n"/>
+      <c r="V11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="Z11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AA11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="125" t="n">
+      <c r="AB11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AE11" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="125" t="n"/>
+      <c r="AH11" s="125" t="n"/>
     </row>
     <row r="12" s="83"/>
     <row r="13" ht="26" customHeight="1" s="83">
@@ -28184,8 +28252,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AF1"/>
     <mergeCell ref="Q14:Q21"/>
+    <mergeCell ref="A1:AH1"/>
   </mergeCells>
   <conditionalFormatting sqref="D12 D14:D19">
     <cfRule type="cellIs" priority="19" operator="greaterThan" dxfId="3">
@@ -28403,7 +28471,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF4:AF9">
+  <conditionalFormatting sqref="AD4:AD9">
     <cfRule type="cellIs" priority="39" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -28411,7 +28479,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF4:AF10">
+  <conditionalFormatting sqref="AD4:AD10">
     <cfRule type="cellIs" priority="41" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -28480,6 +28548,8 @@
       <c r="AB1" s="135" t="n"/>
       <c r="AC1" s="135" t="n"/>
       <c r="AD1" s="135" t="n"/>
+      <c r="AE1" s="135" t="n"/>
+      <c r="AF1" s="135" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="83">
       <c r="A2" s="105" t="n"/>
@@ -28527,51 +28597,61 @@
       <c r="S2" s="105" t="n"/>
       <c r="T2" s="105" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="U2" s="105" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="V2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="W2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="X2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="105" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AA2" s="105" t="n"/>
+      <c r="AB2" s="105" t="n"/>
+      <c r="AC2" s="105" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="U2" s="105" t="inlineStr">
+      <c r="AD2" s="105" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="V2" s="105" t="inlineStr">
+      <c r="AE2" s="105" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="W2" s="105" t="inlineStr">
+      <c r="AF2" s="105" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="X2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Y2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Z2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AA2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AB2" s="105" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AC2" s="105" t="n"/>
-      <c r="AD2" s="105" t="n"/>
     </row>
     <row r="3" ht="52" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -28693,51 +28773,63 @@
           <t>較上週比</t>
         </is>
       </c>
-      <c r="T3" s="86" t="n"/>
-      <c r="U3" s="86" t="n"/>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
-      <c r="X3" s="70" t="inlineStr">
+      <c r="T3" s="70" t="inlineStr">
         <is>
           <t>2025
 04/01~04/18</t>
         </is>
       </c>
-      <c r="Y3" s="71" t="inlineStr">
+      <c r="U3" s="71" t="inlineStr">
         <is>
           <t>2026
 04/01~04/18</t>
         </is>
       </c>
-      <c r="Z3" s="70" t="inlineStr">
+      <c r="V3" s="70" t="inlineStr">
         <is>
           <t>2025
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AA3" s="71" t="inlineStr">
+      <c r="W3" s="71" t="inlineStr">
         <is>
           <t>2026
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AB3" s="70" t="inlineStr">
+      <c r="X3" s="70" t="inlineStr">
         <is>
           <t>2025
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AC3" s="71" t="inlineStr">
+      <c r="Y3" s="71" t="inlineStr">
         <is>
           <t>2026
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AD3" s="86" t="inlineStr">
+      <c r="Z3" s="70" t="inlineStr">
+        <is>
+          <t>2025
+04/01~04/18</t>
+        </is>
+      </c>
+      <c r="AA3" s="71" t="inlineStr">
+        <is>
+          <t>2026
+04/01~04/18</t>
+        </is>
+      </c>
+      <c r="AB3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AC3" s="86" t="n"/>
+      <c r="AD3" s="86" t="n"/>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="41" t="inlineStr">
@@ -28799,35 +28891,41 @@
       <c r="S4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="123" t="n"/>
-      <c r="W4" s="123" t="n"/>
+      <c r="T4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="123" t="n">
+      <c r="Z4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="123" t="n"/>
+      <c r="AF4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="41" t="inlineStr">
@@ -28889,35 +28987,41 @@
       <c r="S5" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
+      <c r="T5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="124" t="n">
+      <c r="Z5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="124" t="n"/>
+      <c r="AF5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="41" t="inlineStr">
@@ -28979,35 +29083,41 @@
       <c r="S6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="123" t="n"/>
-      <c r="W6" s="123" t="n"/>
+      <c r="T6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="123" t="n">
+      <c r="Z6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="123" t="n"/>
+      <c r="AF6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="41" t="inlineStr">
@@ -29069,35 +29179,41 @@
       <c r="S7" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="124" t="n"/>
-      <c r="W7" s="124" t="n"/>
+      <c r="T7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="124" t="n">
+      <c r="Z7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="124" t="n"/>
+      <c r="AF7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="41" t="inlineStr">
@@ -29159,35 +29275,41 @@
       <c r="S8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="123" t="n"/>
-      <c r="W8" s="123" t="n"/>
+      <c r="T8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="123" t="n">
+      <c r="Z8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="123" t="n"/>
+      <c r="AF8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="41" t="inlineStr">
@@ -29249,35 +29371,41 @@
       <c r="S9" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="124" t="n"/>
-      <c r="W9" s="124" t="n"/>
+      <c r="T9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="124" t="n">
+      <c r="Z9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="124" t="n"/>
+      <c r="AF9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="73" t="n"/>
@@ -29299,17 +29427,19 @@
       <c r="Q10" s="124" t="n"/>
       <c r="R10" s="124" t="n"/>
       <c r="S10" s="74" t="n"/>
-      <c r="T10" s="124" t="n"/>
-      <c r="U10" s="124" t="n"/>
-      <c r="V10" s="124" t="n"/>
-      <c r="W10" s="124" t="n"/>
+      <c r="T10" s="46" t="n"/>
+      <c r="U10" s="46" t="n"/>
+      <c r="V10" s="46" t="n"/>
+      <c r="W10" s="46" t="n"/>
       <c r="X10" s="46" t="n"/>
       <c r="Y10" s="46" t="n"/>
-      <c r="Z10" s="46" t="n"/>
-      <c r="AA10" s="46" t="n"/>
-      <c r="AB10" s="124" t="n"/>
+      <c r="Z10" s="124" t="n"/>
+      <c r="AA10" s="124" t="n"/>
+      <c r="AB10" s="74" t="n"/>
       <c r="AC10" s="124" t="n"/>
-      <c r="AD10" s="74" t="n"/>
+      <c r="AD10" s="124" t="n"/>
+      <c r="AE10" s="124" t="n"/>
+      <c r="AF10" s="124" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="83">
       <c r="A11" s="47" t="inlineStr">
@@ -29371,35 +29501,41 @@
       <c r="S11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="125" t="n"/>
-      <c r="W11" s="125" t="n"/>
+      <c r="T11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="X11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="Y11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="125" t="n">
+      <c r="Z11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AC11" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="125" t="n"/>
+      <c r="AF11" s="125" t="n"/>
     </row>
     <row r="12" s="83"/>
     <row r="13" ht="26" customHeight="1" s="83">
@@ -31962,8 +32098,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:AF1"/>
     <mergeCell ref="Q14:Q21"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D10">
     <cfRule type="cellIs" priority="77" operator="greaterThan" dxfId="3">
@@ -32181,7 +32317,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD9">
+  <conditionalFormatting sqref="AB4:AB9">
     <cfRule type="cellIs" priority="73" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -32189,7 +32325,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD10">
+  <conditionalFormatting sqref="AB4:AB10">
     <cfRule type="cellIs" priority="75" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -32268,51 +32404,61 @@
       <c r="S2" s="105" t="n"/>
       <c r="T2" s="105" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="U2" s="105" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="V2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="W2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="X2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="105" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AA2" s="105" t="n"/>
+      <c r="AB2" s="105" t="n"/>
+      <c r="AC2" s="105" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="U2" s="105" t="inlineStr">
+      <c r="AD2" s="105" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="V2" s="105" t="inlineStr">
+      <c r="AE2" s="105" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="W2" s="105" t="inlineStr">
+      <c r="AF2" s="105" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="X2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Y2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Z2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AA2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AB2" s="105" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AC2" s="105" t="n"/>
-      <c r="AD2" s="105" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -32434,51 +32580,63 @@
           <t>較上週比</t>
         </is>
       </c>
-      <c r="T3" s="86" t="n"/>
-      <c r="U3" s="86" t="n"/>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
-      <c r="X3" s="39" t="inlineStr">
+      <c r="T3" s="39" t="inlineStr">
         <is>
           <t>2025
 01/01~04/18</t>
         </is>
       </c>
-      <c r="Y3" s="40" t="inlineStr">
+      <c r="U3" s="40" t="inlineStr">
         <is>
           <t>2026
 01/01~04/18</t>
         </is>
       </c>
-      <c r="Z3" s="39" t="inlineStr">
+      <c r="V3" s="39" t="inlineStr">
         <is>
           <t>2025
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AA3" s="40" t="inlineStr">
+      <c r="W3" s="40" t="inlineStr">
         <is>
           <t>2026
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AB3" s="39" t="inlineStr">
+      <c r="X3" s="39" t="inlineStr">
         <is>
           <t>2025
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AC3" s="40" t="inlineStr">
+      <c r="Y3" s="40" t="inlineStr">
         <is>
           <t>2026
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AD3" s="86" t="inlineStr">
+      <c r="Z3" s="39" t="inlineStr">
+        <is>
+          <t>2025
+01/01~04/18</t>
+        </is>
+      </c>
+      <c r="AA3" s="40" t="inlineStr">
+        <is>
+          <t>2026
+01/01~04/18</t>
+        </is>
+      </c>
+      <c r="AB3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AC3" s="86" t="n"/>
+      <c r="AD3" s="86" t="n"/>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="41" t="inlineStr">
@@ -32540,35 +32698,41 @@
       <c r="S4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="123" t="n"/>
-      <c r="W4" s="123" t="n"/>
+      <c r="T4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="123" t="n">
+      <c r="Z4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="123" t="n"/>
+      <c r="AF4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="41" t="inlineStr">
@@ -32630,35 +32794,41 @@
       <c r="S5" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
+      <c r="T5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="124" t="n">
+      <c r="Z5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="124" t="n"/>
+      <c r="AF5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="41" t="inlineStr">
@@ -32720,35 +32890,41 @@
       <c r="S6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="123" t="n"/>
-      <c r="W6" s="123" t="n"/>
+      <c r="T6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="123" t="n">
+      <c r="Z6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="123" t="n"/>
+      <c r="AF6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="41" t="inlineStr">
@@ -32810,35 +32986,41 @@
       <c r="S7" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="124" t="n"/>
-      <c r="W7" s="124" t="n"/>
+      <c r="T7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="124" t="n">
+      <c r="Z7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="124" t="n"/>
+      <c r="AF7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="41" t="inlineStr">
@@ -32900,35 +33082,41 @@
       <c r="S8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="123" t="n"/>
-      <c r="W8" s="123" t="n"/>
+      <c r="T8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="123" t="n">
+      <c r="Z8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="123" t="n"/>
+      <c r="AF8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="41" t="inlineStr">
@@ -32990,35 +33178,41 @@
       <c r="S9" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="124" t="n"/>
-      <c r="W9" s="124" t="n"/>
+      <c r="T9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="124" t="n">
+      <c r="Z9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="124" t="n"/>
+      <c r="AF9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="73" t="n"/>
@@ -33040,17 +33234,19 @@
       <c r="Q10" s="124" t="n"/>
       <c r="R10" s="124" t="n"/>
       <c r="S10" s="74" t="n"/>
-      <c r="T10" s="124" t="n"/>
-      <c r="U10" s="124" t="n"/>
-      <c r="V10" s="124" t="n"/>
-      <c r="W10" s="124" t="n"/>
+      <c r="T10" s="46" t="n"/>
+      <c r="U10" s="46" t="n"/>
+      <c r="V10" s="46" t="n"/>
+      <c r="W10" s="46" t="n"/>
       <c r="X10" s="46" t="n"/>
       <c r="Y10" s="46" t="n"/>
-      <c r="Z10" s="46" t="n"/>
-      <c r="AA10" s="46" t="n"/>
-      <c r="AB10" s="124" t="n"/>
+      <c r="Z10" s="124" t="n"/>
+      <c r="AA10" s="124" t="n"/>
+      <c r="AB10" s="74" t="n"/>
       <c r="AC10" s="124" t="n"/>
-      <c r="AD10" s="74" t="n"/>
+      <c r="AD10" s="124" t="n"/>
+      <c r="AE10" s="124" t="n"/>
+      <c r="AF10" s="124" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="83">
       <c r="A11" s="47" t="inlineStr">
@@ -33112,35 +33308,41 @@
       <c r="S11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="125" t="n"/>
-      <c r="W11" s="125" t="n"/>
+      <c r="T11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="X11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="Y11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="125" t="n">
+      <c r="Z11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AC11" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="125" t="n"/>
+      <c r="AF11" s="125" t="n"/>
     </row>
     <row r="12" s="83"/>
     <row r="13" ht="26" customHeight="1" s="83">
@@ -35913,7 +36115,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD9">
+  <conditionalFormatting sqref="AB4:AB9">
     <cfRule type="cellIs" priority="75" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -35921,7 +36123,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD10">
+  <conditionalFormatting sqref="AB4:AB10">
     <cfRule type="cellIs" priority="77" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -43442,51 +43644,61 @@
       <c r="S2" s="105" t="n"/>
       <c r="T2" s="105" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="U2" s="105" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="V2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="W2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="X2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="105" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AA2" s="105" t="n"/>
+      <c r="AB2" s="105" t="n"/>
+      <c r="AC2" s="105" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="U2" s="105" t="inlineStr">
+      <c r="AD2" s="105" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="V2" s="105" t="inlineStr">
+      <c r="AE2" s="105" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="W2" s="105" t="inlineStr">
+      <c r="AF2" s="105" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="X2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Y2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Z2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AA2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AB2" s="105" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AC2" s="105" t="n"/>
-      <c r="AD2" s="105" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -43580,10 +43792,26 @@
           <t>較上週比</t>
         </is>
       </c>
-      <c r="T3" s="86" t="n"/>
-      <c r="U3" s="86" t="n"/>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
+      <c r="T3" s="39" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="U3" s="40" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="V3" s="39" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="W3" s="40" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
       <c r="X3" s="39" t="inlineStr">
         <is>
           <t>W15</t>
@@ -43604,21 +43832,15 @@
           <t>W16</t>
         </is>
       </c>
-      <c r="AB3" s="39" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="AC3" s="40" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="AD3" s="86" t="inlineStr">
+      <c r="AB3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AC3" s="86" t="n"/>
+      <c r="AD3" s="86" t="n"/>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="41" t="inlineStr">
@@ -43680,35 +43902,41 @@
       <c r="S4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="123" t="n"/>
-      <c r="W4" s="123" t="n"/>
+      <c r="T4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="123" t="n">
+      <c r="Z4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="123" t="n"/>
+      <c r="AF4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="41" t="inlineStr">
@@ -43770,35 +43998,41 @@
       <c r="S5" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
+      <c r="T5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="124" t="n">
+      <c r="Z5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="124" t="n"/>
+      <c r="AF5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="41" t="inlineStr">
@@ -43860,35 +44094,41 @@
       <c r="S6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="123" t="n"/>
-      <c r="W6" s="123" t="n"/>
+      <c r="T6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="123" t="n">
+      <c r="Z6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="123" t="n"/>
+      <c r="AF6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="41" t="inlineStr">
@@ -43950,35 +44190,41 @@
       <c r="S7" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="124" t="n"/>
-      <c r="W7" s="124" t="n"/>
+      <c r="T7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="124" t="n">
+      <c r="Z7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="124" t="n"/>
+      <c r="AF7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="41" t="inlineStr">
@@ -44040,35 +44286,41 @@
       <c r="S8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="123" t="n"/>
-      <c r="W8" s="123" t="n"/>
+      <c r="T8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="123" t="n">
+      <c r="Z8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="123" t="n"/>
+      <c r="AF8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="41" t="inlineStr">
@@ -44130,35 +44382,41 @@
       <c r="S9" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="124" t="n"/>
-      <c r="W9" s="124" t="n"/>
+      <c r="T9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="124" t="n">
+      <c r="Z9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="124" t="n"/>
+      <c r="AF9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="73" t="n"/>
@@ -44180,17 +44438,19 @@
       <c r="Q10" s="124" t="n"/>
       <c r="R10" s="124" t="n"/>
       <c r="S10" s="74" t="n"/>
-      <c r="T10" s="124" t="n"/>
-      <c r="U10" s="124" t="n"/>
-      <c r="V10" s="124" t="n"/>
-      <c r="W10" s="124" t="n"/>
+      <c r="T10" s="46" t="n"/>
+      <c r="U10" s="46" t="n"/>
+      <c r="V10" s="46" t="n"/>
+      <c r="W10" s="46" t="n"/>
       <c r="X10" s="46" t="n"/>
       <c r="Y10" s="46" t="n"/>
-      <c r="Z10" s="46" t="n"/>
-      <c r="AA10" s="46" t="n"/>
-      <c r="AB10" s="124" t="n"/>
+      <c r="Z10" s="124" t="n"/>
+      <c r="AA10" s="124" t="n"/>
+      <c r="AB10" s="74" t="n"/>
       <c r="AC10" s="124" t="n"/>
-      <c r="AD10" s="74" t="n"/>
+      <c r="AD10" s="124" t="n"/>
+      <c r="AE10" s="124" t="n"/>
+      <c r="AF10" s="124" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="83">
       <c r="A11" s="47" t="inlineStr">
@@ -44252,35 +44512,41 @@
       <c r="S11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="125" t="n"/>
-      <c r="W11" s="125" t="n"/>
+      <c r="T11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="X11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="Y11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="125" t="n">
+      <c r="Z11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AC11" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD11" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="125" t="n"/>
+      <c r="AF11" s="125" t="n"/>
     </row>
     <row r="12" s="83"/>
     <row r="13" ht="26" customHeight="1" s="83">
@@ -47039,7 +47305,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD9">
+  <conditionalFormatting sqref="AB4:AB9">
     <cfRule type="cellIs" priority="87" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -47047,7 +47313,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD10">
+  <conditionalFormatting sqref="AB4:AB10">
     <cfRule type="cellIs" priority="89" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
